--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R350"/>
+  <dimension ref="A1:R351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21450,6 +21450,66 @@
       <c r="R350" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>331.48</v>
+      </c>
+      <c r="C351" t="n">
+        <v>321.08</v>
+      </c>
+      <c r="D351" t="n">
+        <v>324.14</v>
+      </c>
+      <c r="E351" t="n">
+        <v>321.48</v>
+      </c>
+      <c r="F351" t="n">
+        <v>334.01</v>
+      </c>
+      <c r="G351" t="n">
+        <v>339.34</v>
+      </c>
+      <c r="H351" t="n">
+        <v>331.19</v>
+      </c>
+      <c r="I351" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="J351" t="n">
+        <v>321.07</v>
+      </c>
+      <c r="K351" t="n">
+        <v>321.33</v>
+      </c>
+      <c r="L351" t="n">
+        <v>321.91</v>
+      </c>
+      <c r="M351" t="n">
+        <v>309.47</v>
+      </c>
+      <c r="N351" t="n">
+        <v>318.62</v>
+      </c>
+      <c r="O351" t="n">
+        <v>304.9</v>
+      </c>
+      <c r="P351" t="n">
+        <v>311.91</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>312.93</v>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21464,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25147,6 +25207,16 @@
       </c>
       <c r="B368" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -25315,28 +25385,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6364279340343866</v>
+        <v>-0.6364275707726793</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06645868196757332</v>
+        <v>0.06681140037926103</v>
       </c>
       <c r="M2" t="n">
-        <v>9.582847413645199</v>
+        <v>9.555154445063788</v>
       </c>
       <c r="N2" t="n">
-        <v>311.5367743711927</v>
+        <v>310.6363790708156</v>
       </c>
       <c r="O2" t="n">
-        <v>17.65040436848949</v>
+        <v>17.62487954769665</v>
       </c>
       <c r="P2" t="n">
-        <v>348.0298740647287</v>
+        <v>348.0298703075487</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25393,28 +25463,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3697994779718637</v>
+        <v>-0.3691475833284758</v>
       </c>
       <c r="J3" t="n">
+        <v>350</v>
+      </c>
+      <c r="K3" t="n">
         <v>349</v>
       </c>
-      <c r="K3" t="n">
-        <v>348</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2568086943597997</v>
+        <v>0.2571767610190457</v>
       </c>
       <c r="M3" t="n">
-        <v>3.594635651330415</v>
+        <v>3.587623970427992</v>
       </c>
       <c r="N3" t="n">
-        <v>21.94820562752275</v>
+        <v>21.88949018104335</v>
       </c>
       <c r="O3" t="n">
-        <v>4.684891207650691</v>
+        <v>4.678620542536374</v>
       </c>
       <c r="P3" t="n">
-        <v>329.4812685861942</v>
+        <v>329.4745984562334</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25471,28 +25541,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3230741068797695</v>
+        <v>-0.3240233932335261</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1988553871782774</v>
+        <v>0.2006361425499764</v>
       </c>
       <c r="M4" t="n">
-        <v>3.463660917957894</v>
+        <v>3.459055112943133</v>
       </c>
       <c r="N4" t="n">
-        <v>23.26062631640918</v>
+        <v>23.20298553600636</v>
       </c>
       <c r="O4" t="n">
-        <v>4.822927152301721</v>
+        <v>4.816947740634765</v>
       </c>
       <c r="P4" t="n">
-        <v>334.3067809464914</v>
+        <v>334.3165040113113</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25549,28 +25619,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7076775308286515</v>
+        <v>-0.7078476126095078</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5264137123052846</v>
+        <v>0.5279396349676408</v>
       </c>
       <c r="M5" t="n">
-        <v>3.922077445077616</v>
+        <v>3.911785556617101</v>
       </c>
       <c r="N5" t="n">
-        <v>24.92219461135292</v>
+        <v>24.85127141419312</v>
       </c>
       <c r="O5" t="n">
-        <v>4.99221339801825</v>
+        <v>4.985104955183303</v>
       </c>
       <c r="P5" t="n">
-        <v>340.1917525876361</v>
+        <v>340.1934946501586</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25627,28 +25697,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5302606636883376</v>
+        <v>-0.5296103178695246</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L6" t="n">
-        <v>0.536918592684829</v>
+        <v>0.5376367659981545</v>
       </c>
       <c r="M6" t="n">
-        <v>2.761387522189586</v>
+        <v>2.756896127756414</v>
       </c>
       <c r="N6" t="n">
-        <v>13.41440045924459</v>
+        <v>13.38021237568704</v>
       </c>
       <c r="O6" t="n">
-        <v>3.662567468217423</v>
+        <v>3.657897261499705</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5893509557843</v>
+        <v>346.5826897891861</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25705,28 +25775,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5447074772524628</v>
+        <v>-0.5443192967433153</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>0.565014821034744</v>
+        <v>0.5660246128980042</v>
       </c>
       <c r="M7" t="n">
-        <v>2.751111750490012</v>
+        <v>2.745414179258067</v>
       </c>
       <c r="N7" t="n">
-        <v>12.63527903617091</v>
+        <v>12.60065275853271</v>
       </c>
       <c r="O7" t="n">
-        <v>3.554613767509899</v>
+        <v>3.549739815610816</v>
       </c>
       <c r="P7" t="n">
-        <v>352.7791957452238</v>
+        <v>352.7752198066281</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25783,28 +25853,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4276475503260987</v>
+        <v>-0.4278329207177673</v>
       </c>
       <c r="J8" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K8" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3999610019258222</v>
+        <v>0.4015212584298063</v>
       </c>
       <c r="M8" t="n">
-        <v>2.939595479621034</v>
+        <v>2.932139581898159</v>
       </c>
       <c r="N8" t="n">
-        <v>15.17670004017652</v>
+        <v>15.13367429125684</v>
       </c>
       <c r="O8" t="n">
-        <v>3.895728435116662</v>
+        <v>3.890202345798588</v>
       </c>
       <c r="P8" t="n">
-        <v>342.655771086842</v>
+        <v>342.65766974295</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25861,28 +25931,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6539885465551194</v>
+        <v>-0.6522875670488015</v>
       </c>
       <c r="J9" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5695905234688585</v>
+        <v>0.5693102659381869</v>
       </c>
       <c r="M9" t="n">
-        <v>3.348555151749599</v>
+        <v>3.347353302383125</v>
       </c>
       <c r="N9" t="n">
-        <v>17.87733994334851</v>
+        <v>17.85457452770179</v>
       </c>
       <c r="O9" t="n">
-        <v>4.228160349767794</v>
+        <v>4.225467373877332</v>
       </c>
       <c r="P9" t="n">
-        <v>340.1024509871687</v>
+        <v>340.0850287057551</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25939,28 +26009,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4617380708234147</v>
+        <v>-0.4622105802642727</v>
       </c>
       <c r="J10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4069388876635752</v>
+        <v>0.4087672748743728</v>
       </c>
       <c r="M10" t="n">
-        <v>3.159412471993372</v>
+        <v>3.153098680865869</v>
       </c>
       <c r="N10" t="n">
-        <v>17.18720140276932</v>
+        <v>17.14027987478821</v>
       </c>
       <c r="O10" t="n">
-        <v>4.145744975606836</v>
+        <v>4.140082109667417</v>
       </c>
       <c r="P10" t="n">
-        <v>333.9557403167132</v>
+        <v>333.9605799943334</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26017,28 +26087,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2602663430641844</v>
+        <v>-0.2602061237970373</v>
       </c>
       <c r="J11" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K11" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2748533941209204</v>
+        <v>0.2758882463371954</v>
       </c>
       <c r="M11" t="n">
-        <v>2.239003639958435</v>
+        <v>2.232865272248146</v>
       </c>
       <c r="N11" t="n">
-        <v>9.885628321505113</v>
+        <v>9.857419154911621</v>
       </c>
       <c r="O11" t="n">
-        <v>3.144141905433836</v>
+        <v>3.139652712468629</v>
       </c>
       <c r="P11" t="n">
-        <v>327.9856480977961</v>
+        <v>327.9850313019941</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26095,28 +26165,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1020587848089839</v>
+        <v>-0.1014580151633844</v>
       </c>
       <c r="J12" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K12" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04736959807212582</v>
+        <v>0.04707889720664282</v>
       </c>
       <c r="M12" t="n">
-        <v>2.54884763773116</v>
+        <v>2.544434925514512</v>
       </c>
       <c r="N12" t="n">
-        <v>11.58694824939596</v>
+        <v>11.55737450705814</v>
       </c>
       <c r="O12" t="n">
-        <v>3.403960670953171</v>
+        <v>3.399613876171549</v>
       </c>
       <c r="P12" t="n">
-        <v>323.4428280926522</v>
+        <v>323.4366747099739</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26173,28 +26243,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2794995886462754</v>
+        <v>-0.2801589962685259</v>
       </c>
       <c r="J13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2454780859659066</v>
+        <v>0.2473432233619256</v>
       </c>
       <c r="M13" t="n">
-        <v>2.640893733248241</v>
+        <v>2.636431021912672</v>
       </c>
       <c r="N13" t="n">
-        <v>13.28204720160997</v>
+        <v>13.24835341167869</v>
       </c>
       <c r="O13" t="n">
-        <v>3.644454307795609</v>
+        <v>3.639828761312637</v>
       </c>
       <c r="P13" t="n">
-        <v>317.9651489209887</v>
+        <v>317.9719029031023</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26251,28 +26321,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3686474749365121</v>
+        <v>-0.3673885941046251</v>
       </c>
       <c r="J14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L14" t="n">
-        <v>0.394901605696761</v>
+        <v>0.394295270325621</v>
       </c>
       <c r="M14" t="n">
-        <v>2.683616321678768</v>
+        <v>2.681980123927549</v>
       </c>
       <c r="N14" t="n">
-        <v>11.51869215804037</v>
+        <v>11.50128948585623</v>
       </c>
       <c r="O14" t="n">
-        <v>3.393919880910621</v>
+        <v>3.391355110550387</v>
       </c>
       <c r="P14" t="n">
-        <v>325.860636357111</v>
+        <v>325.8477422710636</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26329,28 +26399,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3958044129451458</v>
+        <v>-0.3942316460597599</v>
       </c>
       <c r="J15" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K15" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2199386348889416</v>
+        <v>0.2194072486888494</v>
       </c>
       <c r="M15" t="n">
-        <v>4.239020949040483</v>
+        <v>4.235042121190294</v>
       </c>
       <c r="N15" t="n">
-        <v>30.73491746988108</v>
+        <v>30.67130879492171</v>
       </c>
       <c r="O15" t="n">
-        <v>5.543908140462023</v>
+        <v>5.538168361012665</v>
       </c>
       <c r="P15" t="n">
-        <v>312.2643065524675</v>
+        <v>312.2481974887348</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26407,28 +26477,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3683008555485529</v>
+        <v>-0.3676498018808695</v>
       </c>
       <c r="J16" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K16" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2338197544464696</v>
+        <v>0.2341683437685684</v>
       </c>
       <c r="M16" t="n">
-        <v>3.826389991018909</v>
+        <v>3.819119866424509</v>
       </c>
       <c r="N16" t="n">
-        <v>24.58661549693251</v>
+        <v>24.52051581332867</v>
       </c>
       <c r="O16" t="n">
-        <v>4.958489235334943</v>
+        <v>4.951819444742373</v>
       </c>
       <c r="P16" t="n">
-        <v>320.2803020823167</v>
+        <v>320.2736336655771</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26485,28 +26555,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4124905112918723</v>
+        <v>-0.4125984777533058</v>
       </c>
       <c r="J17" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K17" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2454939608236333</v>
+        <v>0.2466389778363068</v>
       </c>
       <c r="M17" t="n">
-        <v>4.172272360947948</v>
+        <v>4.160910923818362</v>
       </c>
       <c r="N17" t="n">
-        <v>28.92633267510354</v>
+        <v>28.8438000775322</v>
       </c>
       <c r="O17" t="n">
-        <v>5.378320618474092</v>
+        <v>5.370642426891982</v>
       </c>
       <c r="P17" t="n">
-        <v>323.8538497235043</v>
+        <v>323.8549555699107</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26544,7 +26614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R350"/>
+  <dimension ref="A1:R351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58727,6 +58797,98 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-38.79518131739534,174.59168355791573</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-38.794520652790744,174.59200778503163</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-38.793833373942014,174.5921808290683</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-38.79315739576819,174.59241811942547</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-38.79245138400885,174.59248480037598</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-38.791757352825115,174.59263312711755</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-38.791082571837954,174.59290616454135</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-38.79040371239282,174.59313826665286</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-38.78972575473941,174.59337317353865</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-38.78903872624122,174.5935464192315</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-38.788351158932564,174.59371604460512</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-38.787710811476714,174.59402514088455</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-38.78705138270552,174.59419834717335</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-38.78643693304294,174.59465078669314</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-38.78575755988424,174.59487952688875</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>-38.78509589463747,174.59517339908473</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R351"/>
+  <dimension ref="A1:R352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21510,6 +21510,66 @@
       <c r="R351" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>332.74</v>
+      </c>
+      <c r="C352" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="D352" t="n">
+        <v>323.75</v>
+      </c>
+      <c r="E352" t="n">
+        <v>322.24</v>
+      </c>
+      <c r="F352" t="n">
+        <v>334.17</v>
+      </c>
+      <c r="G352" t="n">
+        <v>339.17</v>
+      </c>
+      <c r="H352" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="I352" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="J352" t="n">
+        <v>321.36</v>
+      </c>
+      <c r="K352" t="n">
+        <v>321.34</v>
+      </c>
+      <c r="L352" t="n">
+        <v>321.42</v>
+      </c>
+      <c r="M352" t="n">
+        <v>308.54</v>
+      </c>
+      <c r="N352" t="n">
+        <v>318.05</v>
+      </c>
+      <c r="O352" t="n">
+        <v>303.97</v>
+      </c>
+      <c r="P352" t="n">
+        <v>311.43</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>312.55</v>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21524,7 +21584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25217,6 +25277,16 @@
       </c>
       <c r="B369" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
@@ -25385,28 +25455,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6364275707726793</v>
+        <v>-0.6357029879928661</v>
       </c>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06681140037926103</v>
+        <v>0.06702571443659211</v>
       </c>
       <c r="M2" t="n">
-        <v>9.555154445063788</v>
+        <v>9.5338257954459</v>
       </c>
       <c r="N2" t="n">
-        <v>310.6363790708156</v>
+        <v>309.746207020482</v>
       </c>
       <c r="O2" t="n">
-        <v>17.62487954769665</v>
+        <v>17.59960814962884</v>
       </c>
       <c r="P2" t="n">
-        <v>348.0298703075487</v>
+        <v>348.0223357811421</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25463,28 +25533,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3691475833284758</v>
+        <v>-0.3681435812707685</v>
       </c>
       <c r="J3" t="n">
+        <v>351</v>
+      </c>
+      <c r="K3" t="n">
         <v>350</v>
       </c>
-      <c r="K3" t="n">
-        <v>349</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2571767610190457</v>
+        <v>0.2571391936954283</v>
       </c>
       <c r="M3" t="n">
-        <v>3.587623970427992</v>
+        <v>3.58236936015284</v>
       </c>
       <c r="N3" t="n">
-        <v>21.88949018104335</v>
+        <v>21.83678241223399</v>
       </c>
       <c r="O3" t="n">
-        <v>4.678620542536374</v>
+        <v>4.672984315427775</v>
       </c>
       <c r="P3" t="n">
-        <v>329.4745984562334</v>
+        <v>329.4642700672371</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25541,28 +25611,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3240233932335261</v>
+        <v>-0.3251580376757516</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2006361425499764</v>
+        <v>0.2025929623107051</v>
       </c>
       <c r="M4" t="n">
-        <v>3.459055112943133</v>
+        <v>3.455447992697004</v>
       </c>
       <c r="N4" t="n">
-        <v>23.20298553600636</v>
+        <v>23.14939484118927</v>
       </c>
       <c r="O4" t="n">
-        <v>4.816947740634765</v>
+        <v>4.811381801643814</v>
       </c>
       <c r="P4" t="n">
-        <v>334.3165040113113</v>
+        <v>334.328188117294</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25619,28 +25689,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7078476126095078</v>
+        <v>-0.7075629380796608</v>
       </c>
       <c r="J5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5279396349676408</v>
+        <v>0.5291531703164245</v>
       </c>
       <c r="M5" t="n">
-        <v>3.911785556617101</v>
+        <v>3.902115038442459</v>
       </c>
       <c r="N5" t="n">
-        <v>24.85127141419312</v>
+        <v>24.78125783723959</v>
       </c>
       <c r="O5" t="n">
-        <v>4.985104955183303</v>
+        <v>4.978077725110325</v>
       </c>
       <c r="P5" t="n">
-        <v>340.1934946501586</v>
+        <v>340.1905631878842</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25697,28 +25767,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5296103178695246</v>
+        <v>-0.5288456853112222</v>
       </c>
       <c r="J6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5376367659981545</v>
+        <v>0.5382310281641707</v>
       </c>
       <c r="M6" t="n">
-        <v>2.756896127756414</v>
+        <v>2.753005872327012</v>
       </c>
       <c r="N6" t="n">
-        <v>13.38021237568704</v>
+        <v>13.34777547871267</v>
       </c>
       <c r="O6" t="n">
-        <v>3.657897261499705</v>
+        <v>3.653460753684466</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5826897891861</v>
+        <v>346.5748159147666</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25775,28 +25845,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5443192967433153</v>
+        <v>-0.5439948105002127</v>
       </c>
       <c r="J7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5660246128980042</v>
+        <v>0.5671130294369189</v>
       </c>
       <c r="M7" t="n">
-        <v>2.745414179258067</v>
+        <v>2.73937616281783</v>
       </c>
       <c r="N7" t="n">
-        <v>12.60065275853271</v>
+        <v>12.56577697423397</v>
       </c>
       <c r="O7" t="n">
-        <v>3.549739815610816</v>
+        <v>3.544823969428379</v>
       </c>
       <c r="P7" t="n">
-        <v>352.7752198066281</v>
+        <v>352.7718783795579</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25853,28 +25923,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4278329207177673</v>
+        <v>-0.427611768737225</v>
       </c>
       <c r="J8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4015212584298063</v>
+        <v>0.4026369383884868</v>
       </c>
       <c r="M8" t="n">
-        <v>2.932139581898159</v>
+        <v>2.92499289787748</v>
       </c>
       <c r="N8" t="n">
-        <v>15.13367429125684</v>
+        <v>15.09103383477698</v>
       </c>
       <c r="O8" t="n">
-        <v>3.890202345798588</v>
+        <v>3.884717986518067</v>
       </c>
       <c r="P8" t="n">
-        <v>342.65766974295</v>
+        <v>342.6553924099964</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25931,28 +26001,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6522875670488015</v>
+        <v>-0.6506822494715182</v>
       </c>
       <c r="J9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5693102659381869</v>
+        <v>0.5691562901071886</v>
       </c>
       <c r="M9" t="n">
-        <v>3.347353302383125</v>
+        <v>3.345691196839073</v>
       </c>
       <c r="N9" t="n">
-        <v>17.85457452770179</v>
+        <v>17.82875761648915</v>
       </c>
       <c r="O9" t="n">
-        <v>4.225467373877332</v>
+        <v>4.222411350933155</v>
       </c>
       <c r="P9" t="n">
-        <v>340.0850287057551</v>
+        <v>340.068497799675</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26009,28 +26079,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4622105802642727</v>
+        <v>-0.462499581060308</v>
       </c>
       <c r="J10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4087672748743728</v>
+        <v>0.4104380481989536</v>
       </c>
       <c r="M10" t="n">
-        <v>3.153098680865869</v>
+        <v>3.145754030793322</v>
       </c>
       <c r="N10" t="n">
-        <v>17.14027987478821</v>
+        <v>17.09225906037423</v>
       </c>
       <c r="O10" t="n">
-        <v>4.140082109667417</v>
+        <v>4.13427854170159</v>
       </c>
       <c r="P10" t="n">
-        <v>333.9605799943334</v>
+        <v>333.9635560067337</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26087,28 +26157,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2602061237970373</v>
+        <v>-0.2601271686724073</v>
       </c>
       <c r="J11" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K11" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2758882463371954</v>
+        <v>0.2769068923010251</v>
       </c>
       <c r="M11" t="n">
-        <v>2.232865272248146</v>
+        <v>2.226839875013118</v>
       </c>
       <c r="N11" t="n">
-        <v>9.857419154911621</v>
+        <v>9.829395937993624</v>
       </c>
       <c r="O11" t="n">
-        <v>3.139652712468629</v>
+        <v>3.135186746908966</v>
       </c>
       <c r="P11" t="n">
-        <v>327.9850313019941</v>
+        <v>327.9842182543028</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26165,28 +26235,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1014580151633844</v>
+        <v>-0.1011199130552401</v>
       </c>
       <c r="J12" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K12" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04707889720664282</v>
+        <v>0.04703109210145928</v>
       </c>
       <c r="M12" t="n">
-        <v>2.544434925514512</v>
+        <v>2.538777455461135</v>
       </c>
       <c r="N12" t="n">
-        <v>11.55737450705814</v>
+        <v>11.52555872335161</v>
       </c>
       <c r="O12" t="n">
-        <v>3.399613876171549</v>
+        <v>3.394931328223239</v>
       </c>
       <c r="P12" t="n">
-        <v>323.4366747099739</v>
+        <v>323.4331930722753</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26243,28 +26313,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2801589962685259</v>
+        <v>-0.2812977467007191</v>
       </c>
       <c r="J13" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K13" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2473432233619256</v>
+        <v>0.2497460845436293</v>
       </c>
       <c r="M13" t="n">
-        <v>2.636431021912672</v>
+        <v>2.634169990854119</v>
       </c>
       <c r="N13" t="n">
-        <v>13.24835341167869</v>
+        <v>13.22321423090202</v>
       </c>
       <c r="O13" t="n">
-        <v>3.639828761312637</v>
+        <v>3.636373774916712</v>
       </c>
       <c r="P13" t="n">
-        <v>317.9719029031023</v>
+        <v>317.9836292908959</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26321,28 +26391,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3673885941046251</v>
+        <v>-0.3664203910437284</v>
       </c>
       <c r="J14" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K14" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L14" t="n">
-        <v>0.394295270325621</v>
+        <v>0.3942079534279903</v>
       </c>
       <c r="M14" t="n">
-        <v>2.681980123927549</v>
+        <v>2.678913218716553</v>
       </c>
       <c r="N14" t="n">
-        <v>11.50128948585623</v>
+        <v>11.47763468342903</v>
       </c>
       <c r="O14" t="n">
-        <v>3.391355110550387</v>
+        <v>3.387865800681756</v>
       </c>
       <c r="P14" t="n">
-        <v>325.8477422710636</v>
+        <v>325.8377721105841</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26399,28 +26469,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3942316460597599</v>
+        <v>-0.3931473470464955</v>
       </c>
       <c r="J15" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K15" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2194072486888494</v>
+        <v>0.2193771571649453</v>
       </c>
       <c r="M15" t="n">
-        <v>4.235042121190294</v>
+        <v>4.228507081830347</v>
       </c>
       <c r="N15" t="n">
-        <v>30.67130879492171</v>
+        <v>30.59535488456735</v>
       </c>
       <c r="O15" t="n">
-        <v>5.538168361012665</v>
+        <v>5.531306797183406</v>
       </c>
       <c r="P15" t="n">
-        <v>312.2481974887348</v>
+        <v>312.2370318194588</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26477,28 +26547,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3676498018808695</v>
+        <v>-0.367244956045294</v>
       </c>
       <c r="J16" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K16" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2341683437685684</v>
+        <v>0.2347853822054854</v>
       </c>
       <c r="M16" t="n">
-        <v>3.819119866424509</v>
+        <v>3.810486845230913</v>
       </c>
       <c r="N16" t="n">
-        <v>24.52051581332867</v>
+        <v>24.4522500273829</v>
       </c>
       <c r="O16" t="n">
-        <v>4.951819444742373</v>
+        <v>4.944921640166091</v>
       </c>
       <c r="P16" t="n">
-        <v>320.2736336655771</v>
+        <v>320.2694647281783</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26555,28 +26625,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4125984777533058</v>
+        <v>-0.4128862147465718</v>
       </c>
       <c r="J17" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K17" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2466389778363068</v>
+        <v>0.2479554775799315</v>
       </c>
       <c r="M17" t="n">
-        <v>4.160910923818362</v>
+        <v>4.15052728019833</v>
       </c>
       <c r="N17" t="n">
-        <v>28.8438000775322</v>
+        <v>28.76242881542483</v>
       </c>
       <c r="O17" t="n">
-        <v>5.370642426891982</v>
+        <v>5.363061515163221</v>
       </c>
       <c r="P17" t="n">
-        <v>323.8549555699107</v>
+        <v>323.8579185681851</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26614,7 +26684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R351"/>
+  <dimension ref="A1:R352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58889,6 +58959,98 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-38.79517882661121,174.59166940550722</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-38.794519427181065,174.59200082120893</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-38.79383414488673,174.59218520949614</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-38.79315589342468,174.59240958328553</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-38.79245106772566,174.5924830033117</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-38.79175766555601,174.59263504293736</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-38.79108137721361,174.5928981348587</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-38.79040409492091,174.5931408688704</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-38.789725272425684,174.59336989251207</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-38.78903870960982,174.59354630609374</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-38.788351973867556,174.59372158830374</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-38.7877128724328,174.59403551758177</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-38.78705301259898,174.5942045693713</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-38.78643968328763,174.59466089898015</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-38.785758979360786,174.59488474608577</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>-38.7850970183837,174.59517753091313</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R352"/>
+  <dimension ref="A1:R353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21570,6 +21570,66 @@
       <c r="R352" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>331.25</v>
+      </c>
+      <c r="C353" t="n">
+        <v>326.14</v>
+      </c>
+      <c r="D353" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="E353" t="n">
+        <v>325.95</v>
+      </c>
+      <c r="F353" t="n">
+        <v>334.29</v>
+      </c>
+      <c r="G353" t="n">
+        <v>340.46</v>
+      </c>
+      <c r="H353" t="n">
+        <v>334.39</v>
+      </c>
+      <c r="I353" t="n">
+        <v>326.45</v>
+      </c>
+      <c r="J353" t="n">
+        <v>321.51</v>
+      </c>
+      <c r="K353" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="L353" t="n">
+        <v>321.32</v>
+      </c>
+      <c r="M353" t="n">
+        <v>310.73</v>
+      </c>
+      <c r="N353" t="n">
+        <v>318.35</v>
+      </c>
+      <c r="O353" t="n">
+        <v>308.81</v>
+      </c>
+      <c r="P353" t="n">
+        <v>311.3</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>312.85</v>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21584,7 +21644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B370"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25287,6 +25347,16 @@
       </c>
       <c r="B370" t="n">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -25455,28 +25525,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6357029879928661</v>
+        <v>-0.6357766245741768</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06702571443659211</v>
+        <v>0.06739965698046568</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5338257954459</v>
+        <v>9.506574507576717</v>
       </c>
       <c r="N2" t="n">
-        <v>309.746207020482</v>
+        <v>308.8561837928651</v>
       </c>
       <c r="O2" t="n">
-        <v>17.59960814962884</v>
+        <v>17.57430464606965</v>
       </c>
       <c r="P2" t="n">
-        <v>348.0223357811421</v>
+        <v>348.0231039198208</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25533,28 +25603,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3681435812707685</v>
+        <v>-0.3647504418916946</v>
       </c>
       <c r="J3" t="n">
+        <v>352</v>
+      </c>
+      <c r="K3" t="n">
         <v>351</v>
       </c>
-      <c r="K3" t="n">
-        <v>350</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2571391936954283</v>
+        <v>0.2537221899007688</v>
       </c>
       <c r="M3" t="n">
-        <v>3.58236936015284</v>
+        <v>3.588924696312422</v>
       </c>
       <c r="N3" t="n">
-        <v>21.83678241223399</v>
+        <v>21.88709096988843</v>
       </c>
       <c r="O3" t="n">
-        <v>4.672984315427775</v>
+        <v>4.678364133956273</v>
       </c>
       <c r="P3" t="n">
-        <v>329.4642700672371</v>
+        <v>329.4292524136143</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25611,28 +25681,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3251580376757516</v>
+        <v>-0.3244864811337573</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2025929623107051</v>
+        <v>0.2028171361431923</v>
       </c>
       <c r="M4" t="n">
-        <v>3.455447992697004</v>
+        <v>3.448999647205474</v>
       </c>
       <c r="N4" t="n">
-        <v>23.14939484118927</v>
+        <v>23.08802146837741</v>
       </c>
       <c r="O4" t="n">
-        <v>4.811381801643814</v>
+        <v>4.80499963250544</v>
       </c>
       <c r="P4" t="n">
-        <v>334.328188117294</v>
+        <v>334.3212506818139</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25689,28 +25759,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7075629380796608</v>
+        <v>-0.7052629722814998</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5291531703164245</v>
+        <v>0.5284350631278262</v>
       </c>
       <c r="M5" t="n">
-        <v>3.902115038442459</v>
+        <v>3.902833897165488</v>
       </c>
       <c r="N5" t="n">
-        <v>24.78125783723959</v>
+        <v>24.76237172763551</v>
       </c>
       <c r="O5" t="n">
-        <v>4.978077725110325</v>
+        <v>4.976180435598724</v>
       </c>
       <c r="P5" t="n">
-        <v>340.1905631878842</v>
+        <v>340.1668036630588</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25767,28 +25837,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5288456853112222</v>
+        <v>-0.5280096075395673</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5382310281641707</v>
+        <v>0.5387371403364636</v>
       </c>
       <c r="M6" t="n">
-        <v>2.753005872327012</v>
+        <v>2.749478562995478</v>
       </c>
       <c r="N6" t="n">
-        <v>13.34777547871267</v>
+        <v>13.31666313479588</v>
       </c>
       <c r="O6" t="n">
-        <v>3.653460753684466</v>
+        <v>3.649200341827765</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5748159147666</v>
+        <v>346.5661789121697</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25845,28 +25915,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5439948105002127</v>
+        <v>-0.5429600417506438</v>
       </c>
       <c r="J7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5671130294369189</v>
+        <v>0.5673762893377883</v>
       </c>
       <c r="M7" t="n">
-        <v>2.73937616281783</v>
+        <v>2.737259090800586</v>
       </c>
       <c r="N7" t="n">
-        <v>12.56577697423397</v>
+        <v>12.54050621945084</v>
       </c>
       <c r="O7" t="n">
-        <v>3.544823969428379</v>
+        <v>3.541257717174908</v>
       </c>
       <c r="P7" t="n">
-        <v>352.7718783795579</v>
+        <v>352.7611888232987</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25923,28 +25993,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.427611768737225</v>
+        <v>-0.4260376935144475</v>
       </c>
       <c r="J8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4026369383884868</v>
+        <v>0.4018517226357767</v>
       </c>
       <c r="M8" t="n">
-        <v>2.92499289787748</v>
+        <v>2.92519373444065</v>
       </c>
       <c r="N8" t="n">
-        <v>15.09103383477698</v>
+        <v>15.0722908129963</v>
       </c>
       <c r="O8" t="n">
-        <v>3.884717986518067</v>
+        <v>3.88230483256999</v>
       </c>
       <c r="P8" t="n">
-        <v>342.6553924099964</v>
+        <v>342.6391316119609</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26001,28 +26071,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6506822494715182</v>
+        <v>-0.6488484101252208</v>
       </c>
       <c r="J9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5691562901071886</v>
+        <v>0.568721501654474</v>
       </c>
       <c r="M9" t="n">
-        <v>3.345691196839073</v>
+        <v>3.345154346990222</v>
       </c>
       <c r="N9" t="n">
-        <v>17.82875761648915</v>
+        <v>17.81085802557371</v>
       </c>
       <c r="O9" t="n">
-        <v>4.222411350933155</v>
+        <v>4.220291225208719</v>
       </c>
       <c r="P9" t="n">
-        <v>340.068497799675</v>
+        <v>340.0495535390652</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26079,28 +26149,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.462499581060308</v>
+        <v>-0.4626848060643496</v>
       </c>
       <c r="J10" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K10" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4104380481989536</v>
+        <v>0.4120102340279299</v>
       </c>
       <c r="M10" t="n">
-        <v>3.145754030793322</v>
+        <v>3.137858267026105</v>
       </c>
       <c r="N10" t="n">
-        <v>17.09225906037423</v>
+        <v>17.04403561800314</v>
       </c>
       <c r="O10" t="n">
-        <v>4.13427854170159</v>
+        <v>4.128442274999511</v>
       </c>
       <c r="P10" t="n">
-        <v>333.9635560067337</v>
+        <v>333.9654694517446</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26157,28 +26227,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2601271686724073</v>
+        <v>-0.2596280529148168</v>
       </c>
       <c r="J11" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K11" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2769068923010251</v>
+        <v>0.2772321017103428</v>
       </c>
       <c r="M11" t="n">
-        <v>2.226839875013118</v>
+        <v>2.222615241076015</v>
       </c>
       <c r="N11" t="n">
-        <v>9.829395937993624</v>
+        <v>9.80389754187582</v>
       </c>
       <c r="O11" t="n">
-        <v>3.135186746908966</v>
+        <v>3.131117618658843</v>
       </c>
       <c r="P11" t="n">
-        <v>327.9842182543028</v>
+        <v>327.9790621979638</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26235,28 +26305,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1011199130552401</v>
+        <v>-0.1008329919574335</v>
       </c>
       <c r="J12" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K12" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04703109210145928</v>
+        <v>0.04702927932815493</v>
       </c>
       <c r="M12" t="n">
-        <v>2.538777455461135</v>
+        <v>2.532902416055665</v>
       </c>
       <c r="N12" t="n">
-        <v>11.52555872335161</v>
+        <v>11.49361736921424</v>
       </c>
       <c r="O12" t="n">
-        <v>3.394931328223239</v>
+        <v>3.390223793382118</v>
       </c>
       <c r="P12" t="n">
-        <v>323.4331930722753</v>
+        <v>323.4302290677881</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26313,28 +26383,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2812977467007191</v>
+        <v>-0.2812384447873918</v>
       </c>
       <c r="J13" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K13" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2497460845436293</v>
+        <v>0.2507382178288161</v>
       </c>
       <c r="M13" t="n">
-        <v>2.634169990854119</v>
+        <v>2.627036898752825</v>
       </c>
       <c r="N13" t="n">
-        <v>13.22321423090202</v>
+        <v>13.18568252896887</v>
       </c>
       <c r="O13" t="n">
-        <v>3.636373774916712</v>
+        <v>3.631209513229562</v>
       </c>
       <c r="P13" t="n">
-        <v>317.9836292908959</v>
+        <v>317.9830166794897</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26391,28 +26461,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3664203910437284</v>
+        <v>-0.3652901354619184</v>
       </c>
       <c r="J14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3942079534279903</v>
+        <v>0.3938371756008178</v>
       </c>
       <c r="M14" t="n">
-        <v>2.678913218716553</v>
+        <v>2.676591559467961</v>
       </c>
       <c r="N14" t="n">
-        <v>11.47763468342903</v>
+        <v>11.45746849715901</v>
       </c>
       <c r="O14" t="n">
-        <v>3.387865800681756</v>
+        <v>3.384888254752143</v>
       </c>
       <c r="P14" t="n">
-        <v>325.8377721105841</v>
+        <v>325.8260961388908</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26469,28 +26539,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3931473470464955</v>
+        <v>-0.3894576608252626</v>
       </c>
       <c r="J15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2193771571649453</v>
+        <v>0.2163979421611638</v>
       </c>
       <c r="M15" t="n">
-        <v>4.228507081830347</v>
+        <v>4.235546706864992</v>
       </c>
       <c r="N15" t="n">
-        <v>30.59535488456735</v>
+        <v>30.64101425201048</v>
       </c>
       <c r="O15" t="n">
-        <v>5.531306797183406</v>
+        <v>5.535432616517925</v>
       </c>
       <c r="P15" t="n">
-        <v>312.2370318194588</v>
+        <v>312.1989159520658</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26547,28 +26617,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.367244956045294</v>
+        <v>-0.3669015867330294</v>
       </c>
       <c r="J16" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K16" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2347853822054854</v>
+        <v>0.2354677573566109</v>
       </c>
       <c r="M16" t="n">
-        <v>3.810486845230913</v>
+        <v>3.801550826961404</v>
       </c>
       <c r="N16" t="n">
-        <v>24.4522500273829</v>
+        <v>24.38393160263048</v>
       </c>
       <c r="O16" t="n">
-        <v>4.944921640166091</v>
+        <v>4.938008870246233</v>
       </c>
       <c r="P16" t="n">
-        <v>320.2694647281783</v>
+        <v>320.2659175920837</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26625,28 +26695,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4128862147465718</v>
+        <v>-0.4129935963376709</v>
       </c>
       <c r="J17" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K17" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2479554775799315</v>
+        <v>0.2491187338590393</v>
       </c>
       <c r="M17" t="n">
-        <v>4.15052728019833</v>
+        <v>4.13927988356424</v>
       </c>
       <c r="N17" t="n">
-        <v>28.76242881542483</v>
+        <v>28.68082966280862</v>
       </c>
       <c r="O17" t="n">
-        <v>5.363061515163221</v>
+        <v>5.355448595851576</v>
       </c>
       <c r="P17" t="n">
-        <v>323.8579185681851</v>
+        <v>323.8590278610196</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26684,7 +26754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R352"/>
+  <dimension ref="A1:R353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59051,6 +59121,98 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-38.7951817720621,174.59168614129197</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-38.794510650222094,174.5919509512593</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-38.79382758196741,174.59214791970305</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-38.7931485596072,174.59236791344935</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-38.79245083051325,174.59248165551352</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-38.79175529247953,174.5926205052463</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-38.791077187611215,174.59286997442427</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-38.79040339639132,174.59313611699494</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-38.78972502295302,174.5933681954294</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-38.789037445621894,174.5935377076228</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-38.788352140180784,174.59372271967084</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-38.78770801921214,174.5940110821344</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-38.78705215476035,174.59420129453025</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-38.786425370176495,174.59460827160228</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-38.7857593638023,174.5948861596183</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-38.785096131215646,174.59517426894334</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R353"/>
+  <dimension ref="A1:R354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21622,14 +21622,74 @@
         <v>308.81</v>
       </c>
       <c r="P353" t="n">
-        <v>311.3</v>
+        <v>316.69</v>
       </c>
       <c r="Q353" t="n">
-        <v>312.85</v>
+        <v>318.97</v>
       </c>
       <c r="R353" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>331.93</v>
+      </c>
+      <c r="C354" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="D354" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="E354" t="n">
+        <v>326.24</v>
+      </c>
+      <c r="F354" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="G354" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="H354" t="n">
+        <v>334.76</v>
+      </c>
+      <c r="I354" t="n">
+        <v>327.73</v>
+      </c>
+      <c r="J354" t="n">
+        <v>322.24</v>
+      </c>
+      <c r="K354" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="L354" t="n">
+        <v>322.04</v>
+      </c>
+      <c r="M354" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="N354" t="n">
+        <v>319.53</v>
+      </c>
+      <c r="O354" t="n">
+        <v>309.42</v>
+      </c>
+      <c r="P354" t="n">
+        <v>317.92</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>321.13</v>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21644,7 +21704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25357,6 +25417,16 @@
       </c>
       <c r="B371" t="n">
         <v>-0.51</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -25525,28 +25595,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6357766245741768</v>
+        <v>-0.6354376831542865</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06739965698046568</v>
+        <v>0.06769673016784539</v>
       </c>
       <c r="M2" t="n">
-        <v>9.506574507576717</v>
+        <v>9.482207834905283</v>
       </c>
       <c r="N2" t="n">
-        <v>308.8561837928651</v>
+        <v>307.9723053900301</v>
       </c>
       <c r="O2" t="n">
-        <v>17.57430464606965</v>
+        <v>17.54913973361743</v>
       </c>
       <c r="P2" t="n">
-        <v>348.0231039198208</v>
+        <v>348.0195497398882</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25603,28 +25673,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3647504418916946</v>
+        <v>-0.3606819039367002</v>
       </c>
       <c r="J3" t="n">
+        <v>353</v>
+      </c>
+      <c r="K3" t="n">
         <v>352</v>
       </c>
-      <c r="K3" t="n">
-        <v>351</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2537221899007688</v>
+        <v>0.2492023220095387</v>
       </c>
       <c r="M3" t="n">
-        <v>3.588924696312422</v>
+        <v>3.59898317705727</v>
       </c>
       <c r="N3" t="n">
-        <v>21.88709096988843</v>
+        <v>21.98566576228405</v>
       </c>
       <c r="O3" t="n">
-        <v>4.678364133956273</v>
+        <v>4.688887475967412</v>
       </c>
       <c r="P3" t="n">
-        <v>329.4292524136143</v>
+        <v>329.3870431377251</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25681,28 +25751,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3244864811337573</v>
+        <v>-0.3226269937041361</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2028171361431923</v>
+        <v>0.2016585230148769</v>
       </c>
       <c r="M4" t="n">
-        <v>3.448999647205474</v>
+        <v>3.448455339843297</v>
       </c>
       <c r="N4" t="n">
-        <v>23.08802146837741</v>
+        <v>23.05607728358586</v>
       </c>
       <c r="O4" t="n">
-        <v>4.80499963250544</v>
+        <v>4.801674424988211</v>
       </c>
       <c r="P4" t="n">
-        <v>334.3212506818139</v>
+        <v>334.3019406555117</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25759,28 +25829,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7052629722814998</v>
+        <v>-0.7027787348751754</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5284350631278262</v>
+        <v>0.5275109792100251</v>
       </c>
       <c r="M5" t="n">
-        <v>3.902833897165488</v>
+        <v>3.904484453479518</v>
       </c>
       <c r="N5" t="n">
-        <v>24.76237172763551</v>
+        <v>24.75194590908187</v>
       </c>
       <c r="O5" t="n">
-        <v>4.976180435598724</v>
+        <v>4.975132752910405</v>
       </c>
       <c r="P5" t="n">
-        <v>340.1668036630588</v>
+        <v>340.1410058604533</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25837,28 +25907,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5280096075395673</v>
+        <v>-0.5275607832121662</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K6" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5387371403364636</v>
+        <v>0.5397104948159559</v>
       </c>
       <c r="M6" t="n">
-        <v>2.749478562995478</v>
+        <v>2.743962878949558</v>
       </c>
       <c r="N6" t="n">
-        <v>13.31666313479588</v>
+        <v>13.28088829420063</v>
       </c>
       <c r="O6" t="n">
-        <v>3.649200341827765</v>
+        <v>3.644295308314164</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5661789121697</v>
+        <v>346.561518052715</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25915,28 +25985,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5429600417506438</v>
+        <v>-0.5411478099653805</v>
       </c>
       <c r="J7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5673762893377883</v>
+        <v>0.5665268603878427</v>
       </c>
       <c r="M7" t="n">
-        <v>2.737259090800586</v>
+        <v>2.73934667227393</v>
       </c>
       <c r="N7" t="n">
-        <v>12.54050621945084</v>
+        <v>12.53676258632104</v>
       </c>
       <c r="O7" t="n">
-        <v>3.541257717174908</v>
+        <v>3.540729103775244</v>
       </c>
       <c r="P7" t="n">
-        <v>352.7611888232987</v>
+        <v>352.7423695277866</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25993,28 +26063,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4260376935144475</v>
+        <v>-0.4242514276677148</v>
       </c>
       <c r="J8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4018517226357767</v>
+        <v>0.400724837497117</v>
       </c>
       <c r="M8" t="n">
-        <v>2.92519373444065</v>
+        <v>2.92643262646237</v>
       </c>
       <c r="N8" t="n">
-        <v>15.0722908129963</v>
+        <v>15.0604707588104</v>
       </c>
       <c r="O8" t="n">
-        <v>3.88230483256999</v>
+        <v>3.880782235427595</v>
       </c>
       <c r="P8" t="n">
-        <v>342.6391316119609</v>
+        <v>342.6205819622384</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26071,28 +26141,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6488484101252208</v>
+        <v>-0.6462994178815503</v>
       </c>
       <c r="J9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.568721501654474</v>
+        <v>0.5673372713739325</v>
       </c>
       <c r="M9" t="n">
-        <v>3.345154346990222</v>
+        <v>3.348042329967185</v>
       </c>
       <c r="N9" t="n">
-        <v>17.81085802557371</v>
+        <v>17.82327894847685</v>
       </c>
       <c r="O9" t="n">
-        <v>4.220291225208719</v>
+        <v>4.221762540512772</v>
       </c>
       <c r="P9" t="n">
-        <v>340.0495535390652</v>
+        <v>340.0230832836146</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26149,28 +26219,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4626848060643496</v>
+        <v>-0.4624509895201632</v>
       </c>
       <c r="J10" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K10" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4120102340279299</v>
+        <v>0.4131548979558176</v>
       </c>
       <c r="M10" t="n">
-        <v>3.137858267026105</v>
+        <v>3.130109472785306</v>
       </c>
       <c r="N10" t="n">
-        <v>17.04403561800314</v>
+        <v>16.9962812881171</v>
       </c>
       <c r="O10" t="n">
-        <v>4.128442274999511</v>
+        <v>4.122654640897913</v>
       </c>
       <c r="P10" t="n">
-        <v>333.9654694517446</v>
+        <v>333.9630413613223</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26227,28 +26297,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2596280529148168</v>
+        <v>-0.258799655458182</v>
       </c>
       <c r="J11" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K11" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2772321017103428</v>
+        <v>0.2769705720235229</v>
       </c>
       <c r="M11" t="n">
-        <v>2.222615241076015</v>
+        <v>2.219751566869696</v>
       </c>
       <c r="N11" t="n">
-        <v>9.80389754187582</v>
+        <v>9.782765401897297</v>
       </c>
       <c r="O11" t="n">
-        <v>3.131117618658843</v>
+        <v>3.127741261980808</v>
       </c>
       <c r="P11" t="n">
-        <v>327.9790621979638</v>
+        <v>327.9704596247915</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26305,28 +26375,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1008329919574335</v>
+        <v>-0.1001534255746198</v>
       </c>
       <c r="J12" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K12" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04702927932815493</v>
+        <v>0.04666538750724469</v>
       </c>
       <c r="M12" t="n">
-        <v>2.532902416055665</v>
+        <v>2.528862433047247</v>
       </c>
       <c r="N12" t="n">
-        <v>11.49361736921424</v>
+        <v>11.46552660343123</v>
       </c>
       <c r="O12" t="n">
-        <v>3.390223793382118</v>
+        <v>3.386078351637958</v>
       </c>
       <c r="P12" t="n">
-        <v>323.4302290677881</v>
+        <v>323.423172045236</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26383,28 +26453,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2812384447873918</v>
+        <v>-0.2801038752818663</v>
       </c>
       <c r="J13" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K13" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2507382178288161</v>
+        <v>0.2501250322872706</v>
       </c>
       <c r="M13" t="n">
-        <v>2.627036898752825</v>
+        <v>2.626213200775211</v>
       </c>
       <c r="N13" t="n">
-        <v>13.18568252896887</v>
+        <v>13.16078634501991</v>
       </c>
       <c r="O13" t="n">
-        <v>3.631209513229562</v>
+        <v>3.627779809335169</v>
       </c>
       <c r="P13" t="n">
-        <v>317.9830166794897</v>
+        <v>317.9712346331879</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26461,28 +26531,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3652901354619184</v>
+        <v>-0.3635088955115197</v>
       </c>
       <c r="J14" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K14" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3938371756008178</v>
+        <v>0.3922400086549023</v>
       </c>
       <c r="M14" t="n">
-        <v>2.676591559467961</v>
+        <v>2.677228159038715</v>
       </c>
       <c r="N14" t="n">
-        <v>11.45746849715901</v>
+        <v>11.45571522050073</v>
       </c>
       <c r="O14" t="n">
-        <v>3.384888254752143</v>
+        <v>3.384629258944135</v>
       </c>
       <c r="P14" t="n">
-        <v>325.8260961388908</v>
+        <v>325.8075986810726</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26539,28 +26609,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3894576608252626</v>
+        <v>-0.3854424980849245</v>
       </c>
       <c r="J15" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K15" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2163979421611638</v>
+        <v>0.2130166887506889</v>
       </c>
       <c r="M15" t="n">
-        <v>4.235546706864992</v>
+        <v>4.244665269251212</v>
       </c>
       <c r="N15" t="n">
-        <v>30.64101425201048</v>
+        <v>30.71022465592808</v>
       </c>
       <c r="O15" t="n">
-        <v>5.535432616517925</v>
+        <v>5.541680670692609</v>
       </c>
       <c r="P15" t="n">
-        <v>312.1989159520658</v>
+        <v>312.1572201078841</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26617,28 +26687,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3669015867330294</v>
+        <v>-0.3600928644762852</v>
       </c>
       <c r="J16" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K16" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2354677573566109</v>
+        <v>0.2280121771955781</v>
       </c>
       <c r="M16" t="n">
-        <v>3.801550826961404</v>
+        <v>3.828048813238814</v>
       </c>
       <c r="N16" t="n">
-        <v>24.38393160263048</v>
+        <v>24.56367513126808</v>
       </c>
       <c r="O16" t="n">
-        <v>4.938008870246233</v>
+        <v>4.956175454043983</v>
       </c>
       <c r="P16" t="n">
-        <v>320.2659175920837</v>
+        <v>320.1953691494621</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26695,28 +26765,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4129935963376709</v>
+        <v>-0.4053513681626804</v>
       </c>
       <c r="J17" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K17" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2491187338590393</v>
+        <v>0.2414576375679066</v>
       </c>
       <c r="M17" t="n">
-        <v>4.13927988356424</v>
+        <v>4.168182731016551</v>
       </c>
       <c r="N17" t="n">
-        <v>28.68082966280862</v>
+        <v>28.88112356222333</v>
       </c>
       <c r="O17" t="n">
-        <v>5.355448595851576</v>
+        <v>5.374116072641465</v>
       </c>
       <c r="P17" t="n">
-        <v>323.8590278610196</v>
+        <v>323.7798448044248</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26754,7 +26824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R353"/>
+  <dimension ref="A1:R354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59199,17 +59269,109 @@
       </c>
       <c r="P353" t="inlineStr">
         <is>
-          <t>-38.7857593638023,174.5948861596183</t>
+          <t>-38.78574342425061,174.5948275523961</t>
         </is>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
-          <t>-38.785096131215646,174.59517426894334</t>
+          <t>-38.785078032966936,174.5951077247761</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-38.79518042782977,174.59167850348402</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-38.79450815945952,174.59193679897837</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-38.79382329234196,174.59212354655867</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-38.7931479863432,174.59236465623877</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-38.79245235262591,174.5924903038853</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-38.79175273544158,174.59260484060346</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-38.79107656505927,174.59286578994232</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-38.79040126753801,174.59312163508935</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-38.789723808852415,174.59335993629378</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-38.78903646436766,174.5935310324942</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-38.788350942725295,174.59371457382795</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-38.78770365352519,174.59398910139217</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-38.78704878059418,174.59418841348946</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-38.78642356624962,174.59460163881437</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-38.7857397868348,174.59481417820976</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>-38.78507164534051,174.59508423860723</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R354"/>
+  <dimension ref="A1:R357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21688,6 +21688,186 @@
         <v>321.13</v>
       </c>
       <c r="R354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>331.65</v>
+      </c>
+      <c r="C355" t="n">
+        <v>326.98</v>
+      </c>
+      <c r="D355" t="n">
+        <v>328.23</v>
+      </c>
+      <c r="E355" t="n">
+        <v>325.72</v>
+      </c>
+      <c r="F355" t="n">
+        <v>332.85</v>
+      </c>
+      <c r="G355" t="n">
+        <v>340.66</v>
+      </c>
+      <c r="H355" t="n">
+        <v>334.02</v>
+      </c>
+      <c r="I355" t="n">
+        <v>329.35</v>
+      </c>
+      <c r="J355" t="n">
+        <v>322.24</v>
+      </c>
+      <c r="K355" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="L355" t="n">
+        <v>322.04</v>
+      </c>
+      <c r="M355" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="N355" t="n">
+        <v>319.53</v>
+      </c>
+      <c r="O355" t="n">
+        <v>309.42</v>
+      </c>
+      <c r="P355" t="n">
+        <v>316.45</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>318.16</v>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>333.96</v>
+      </c>
+      <c r="C356" t="n">
+        <v>327.92</v>
+      </c>
+      <c r="D356" t="n">
+        <v>329.35</v>
+      </c>
+      <c r="E356" t="n">
+        <v>326.34</v>
+      </c>
+      <c r="F356" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="G356" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="H356" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="I356" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="J356" t="n">
+        <v>323.46</v>
+      </c>
+      <c r="K356" t="n">
+        <v>323</v>
+      </c>
+      <c r="L356" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="M356" t="n">
+        <v>312.18</v>
+      </c>
+      <c r="N356" t="n">
+        <v>319.66</v>
+      </c>
+      <c r="O356" t="n">
+        <v>309.77</v>
+      </c>
+      <c r="P356" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>333.96</v>
+      </c>
+      <c r="C357" t="n">
+        <v>327.92</v>
+      </c>
+      <c r="D357" t="n">
+        <v>329.35</v>
+      </c>
+      <c r="E357" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="F357" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="G357" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="H357" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="I357" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="J357" t="n">
+        <v>327.97</v>
+      </c>
+      <c r="K357" t="n">
+        <v>325.25</v>
+      </c>
+      <c r="L357" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="M357" t="n">
+        <v>314.95</v>
+      </c>
+      <c r="N357" t="n">
+        <v>322.86</v>
+      </c>
+      <c r="O357" t="n">
+        <v>309.77</v>
+      </c>
+      <c r="P357" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="R357" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21704,7 +21884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B372"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25427,6 +25607,46 @@
       </c>
       <c r="B372" t="n">
         <v>0.58</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -25595,28 +25815,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6354376831542865</v>
+        <v>-0.6323658687134521</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06769673016784539</v>
+        <v>0.06816081536429586</v>
       </c>
       <c r="M2" t="n">
-        <v>9.482207834905283</v>
+        <v>9.427032666921797</v>
       </c>
       <c r="N2" t="n">
-        <v>307.9723053900301</v>
+        <v>305.3883299451685</v>
       </c>
       <c r="O2" t="n">
-        <v>17.54913973361743</v>
+        <v>17.47536351396355</v>
       </c>
       <c r="P2" t="n">
-        <v>348.0195497398882</v>
+        <v>347.9872262983155</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25673,28 +25893,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3606819039367002</v>
+        <v>-0.3484546034381865</v>
       </c>
       <c r="J3" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2492023220095387</v>
+        <v>0.2355698776450035</v>
       </c>
       <c r="M3" t="n">
-        <v>3.59898317705727</v>
+        <v>3.630982235322842</v>
       </c>
       <c r="N3" t="n">
-        <v>21.98566576228405</v>
+        <v>22.29260209311606</v>
       </c>
       <c r="O3" t="n">
-        <v>4.688887475967412</v>
+        <v>4.721504219326301</v>
       </c>
       <c r="P3" t="n">
-        <v>329.3870431377251</v>
+        <v>329.2598286783386</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25751,28 +25971,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3226269937041361</v>
+        <v>-0.3176002612714295</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2016585230148769</v>
+        <v>0.1987719462449045</v>
       </c>
       <c r="M4" t="n">
-        <v>3.448455339843297</v>
+        <v>3.444692356508374</v>
       </c>
       <c r="N4" t="n">
-        <v>23.05607728358586</v>
+        <v>22.94682686497264</v>
       </c>
       <c r="O4" t="n">
-        <v>4.801674424988211</v>
+        <v>4.790284632980867</v>
       </c>
       <c r="P4" t="n">
-        <v>334.3019406555117</v>
+        <v>334.249584822966</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25829,28 +26049,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7027787348751754</v>
+        <v>-0.6938336922611156</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5275109792100251</v>
+        <v>0.5224703012573831</v>
       </c>
       <c r="M5" t="n">
-        <v>3.904484453479518</v>
+        <v>3.917250987860898</v>
       </c>
       <c r="N5" t="n">
-        <v>24.75194590908187</v>
+        <v>24.83187010997232</v>
       </c>
       <c r="O5" t="n">
-        <v>4.975132752910405</v>
+        <v>4.983158647883119</v>
       </c>
       <c r="P5" t="n">
-        <v>340.1410058604533</v>
+        <v>340.0478256274212</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25907,28 +26127,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5275607832121662</v>
+        <v>-0.5268492392406355</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5397104948159559</v>
+        <v>0.5432465419031258</v>
       </c>
       <c r="M6" t="n">
-        <v>2.743962878949558</v>
+        <v>2.724387810735494</v>
       </c>
       <c r="N6" t="n">
-        <v>13.28088829420063</v>
+        <v>13.17096112972076</v>
       </c>
       <c r="O6" t="n">
-        <v>3.644295308314164</v>
+        <v>3.629181881598214</v>
       </c>
       <c r="P6" t="n">
-        <v>346.561518052715</v>
+        <v>346.5541043989777</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25985,28 +26205,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5411478099653805</v>
+        <v>-0.5375815593935661</v>
       </c>
       <c r="J7" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5665268603878427</v>
+        <v>0.5666551076699651</v>
       </c>
       <c r="M7" t="n">
-        <v>2.73934667227393</v>
+        <v>2.735356959998388</v>
       </c>
       <c r="N7" t="n">
-        <v>12.53676258632104</v>
+        <v>12.4727862475869</v>
       </c>
       <c r="O7" t="n">
-        <v>3.540729103775244</v>
+        <v>3.531683203174784</v>
       </c>
       <c r="P7" t="n">
-        <v>352.7423695277866</v>
+        <v>352.7052315992531</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26063,28 +26283,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4242514276677148</v>
+        <v>-0.4204178247446474</v>
       </c>
       <c r="J8" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.400724837497117</v>
+        <v>0.3996963321020772</v>
       </c>
       <c r="M8" t="n">
-        <v>2.92643262646237</v>
+        <v>2.921927636761279</v>
       </c>
       <c r="N8" t="n">
-        <v>15.0604707588104</v>
+        <v>14.98176413805634</v>
       </c>
       <c r="O8" t="n">
-        <v>3.880782235427595</v>
+        <v>3.870628390591939</v>
       </c>
       <c r="P8" t="n">
-        <v>342.6205819622384</v>
+        <v>342.5806635375027</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26141,28 +26361,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6462994178815503</v>
+        <v>-0.635117460395623</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5673372713739325</v>
+        <v>0.5572899704295643</v>
       </c>
       <c r="M9" t="n">
-        <v>3.348042329967185</v>
+        <v>3.374261039087752</v>
       </c>
       <c r="N9" t="n">
-        <v>17.82327894847685</v>
+        <v>18.08448386707032</v>
       </c>
       <c r="O9" t="n">
-        <v>4.221762540512772</v>
+        <v>4.252585550823207</v>
       </c>
       <c r="P9" t="n">
-        <v>340.0230832836146</v>
+        <v>339.9066316034454</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26219,28 +26439,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4624509895201632</v>
+        <v>-0.4580493708153058</v>
       </c>
       <c r="J10" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4131548979558176</v>
+        <v>0.4110173565919296</v>
       </c>
       <c r="M10" t="n">
-        <v>3.130109472785306</v>
+        <v>3.125161981606157</v>
       </c>
       <c r="N10" t="n">
-        <v>16.9962812881171</v>
+        <v>16.96784923809906</v>
       </c>
       <c r="O10" t="n">
-        <v>4.122654640897913</v>
+        <v>4.119204927907697</v>
       </c>
       <c r="P10" t="n">
-        <v>333.9630413613223</v>
+        <v>333.917159042057</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26297,28 +26517,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.258799655458182</v>
+        <v>-0.2548431248968056</v>
       </c>
       <c r="J11" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2769705720235229</v>
+        <v>0.2729609873597658</v>
       </c>
       <c r="M11" t="n">
-        <v>2.219751566869696</v>
+        <v>2.217167711758869</v>
       </c>
       <c r="N11" t="n">
-        <v>9.782765401897297</v>
+        <v>9.762540724635494</v>
       </c>
       <c r="O11" t="n">
-        <v>3.127741261980808</v>
+        <v>3.124506476971282</v>
       </c>
       <c r="P11" t="n">
-        <v>327.9704596247915</v>
+        <v>327.9292385399401</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26375,28 +26595,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1001534255746198</v>
+        <v>-0.09701914567227864</v>
       </c>
       <c r="J12" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K12" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04666538750724469</v>
+        <v>0.0444825941082766</v>
       </c>
       <c r="M12" t="n">
-        <v>2.528862433047247</v>
+        <v>2.521886321522935</v>
       </c>
       <c r="N12" t="n">
-        <v>11.46552660343123</v>
+        <v>11.41098851653118</v>
       </c>
       <c r="O12" t="n">
-        <v>3.386078351637958</v>
+        <v>3.37801547014385</v>
       </c>
       <c r="P12" t="n">
-        <v>323.423172045236</v>
+        <v>323.3905165190126</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26453,28 +26673,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2801038752818663</v>
+        <v>-0.2758530612156769</v>
       </c>
       <c r="J13" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2501250322872706</v>
+        <v>0.2465885627417058</v>
       </c>
       <c r="M13" t="n">
-        <v>2.626213200775211</v>
+        <v>2.628711171083166</v>
       </c>
       <c r="N13" t="n">
-        <v>13.16078634501991</v>
+        <v>13.12123684953056</v>
       </c>
       <c r="O13" t="n">
-        <v>3.627779809335169</v>
+        <v>3.622324785207776</v>
       </c>
       <c r="P13" t="n">
-        <v>317.9712346331879</v>
+        <v>317.9269530464531</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26531,28 +26751,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3635088955115197</v>
+        <v>-0.356454934031223</v>
       </c>
       <c r="J14" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K14" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3922400086549023</v>
+        <v>0.383204650864843</v>
       </c>
       <c r="M14" t="n">
-        <v>2.677228159038715</v>
+        <v>2.687003558737541</v>
       </c>
       <c r="N14" t="n">
-        <v>11.45571522050073</v>
+        <v>11.54195721157204</v>
       </c>
       <c r="O14" t="n">
-        <v>3.384629258944135</v>
+        <v>3.397345612617598</v>
       </c>
       <c r="P14" t="n">
-        <v>325.8075986810726</v>
+        <v>325.7341174784907</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26609,28 +26829,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3854424980849245</v>
+        <v>-0.3733240962541868</v>
       </c>
       <c r="J15" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K15" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2130166887506889</v>
+        <v>0.2027321248094998</v>
       </c>
       <c r="M15" t="n">
-        <v>4.244665269251212</v>
+        <v>4.274766971098821</v>
       </c>
       <c r="N15" t="n">
-        <v>30.71022465592808</v>
+        <v>30.93240000656035</v>
       </c>
       <c r="O15" t="n">
-        <v>5.541680670692609</v>
+        <v>5.561690391109555</v>
       </c>
       <c r="P15" t="n">
-        <v>312.1572201078841</v>
+        <v>312.0310238369411</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26687,28 +26907,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3600928644762852</v>
+        <v>-0.3507919270533607</v>
       </c>
       <c r="J16" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K16" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2280121771955781</v>
+        <v>0.2198780680175435</v>
       </c>
       <c r="M16" t="n">
-        <v>3.828048813238814</v>
+        <v>3.848018799046832</v>
       </c>
       <c r="N16" t="n">
-        <v>24.56367513126808</v>
+        <v>24.63993940724628</v>
       </c>
       <c r="O16" t="n">
-        <v>4.956175454043983</v>
+        <v>4.96386335501354</v>
       </c>
       <c r="P16" t="n">
-        <v>320.1953691494621</v>
+        <v>320.0985135351729</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26765,28 +26985,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4053513681626804</v>
+        <v>-0.3970300408905354</v>
       </c>
       <c r="J17" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K17" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2414576375679066</v>
+        <v>0.2355944831351373</v>
       </c>
       <c r="M17" t="n">
-        <v>4.168182731016551</v>
+        <v>4.178299468040692</v>
       </c>
       <c r="N17" t="n">
-        <v>28.88112356222333</v>
+        <v>28.8645846891118</v>
       </c>
       <c r="O17" t="n">
-        <v>5.374116072641465</v>
+        <v>5.372577099410655</v>
       </c>
       <c r="P17" t="n">
-        <v>323.7798448044248</v>
+        <v>323.6931891982242</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26824,7 +27044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R354"/>
+  <dimension ref="A1:R357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59375,6 +59595,282 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-38.79518098133725,174.59168164846375</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-38.794508989713904,174.59194151640523</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-38.79382528889638,174.5921348907407</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-38.79314901426479,174.59237049675434</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-38.79245367706106,174.59249782909222</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-38.79175492456053,174.59261825134078</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-38.79107781016301,174.59287415890628</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-38.79039857320548,174.59310330642873</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-38.789723808852415,174.59335993629378</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-38.78903646436766,174.5935310324942</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-38.788350942725295,174.59371457382795</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-38.78770365352519,174.59398910139217</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-38.78704878059418,174.59418841348946</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-38.78642356624962,174.59460163881437</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-38.7857441339901,174.59483016199357</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-38.7850804283256,174.5951165320905</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-38.795176414897945,174.59165570238244</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-38.794507131525265,174.59193095835477</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-38.793823074895364,174.5921223110537</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-38.79314778866594,174.59236353306272</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-38.792452886353566,174.59249333643135</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-38.791754703809104,174.59261689899748</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-38.7910781971546,174.59287676007085</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-38.79039681024557,174.59309131360212</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-38.78972177980624,174.5933461333554</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-38.78903594879325,174.59352752522335</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-38.788351092407254,174.59371559205832</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-38.78770480588967,174.59399490341525</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-38.787048408863924,174.59418699439183</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-38.786422531209425,174.59459783311652</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-38.78574354254053,174.594827987329</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>-38.78507957072813,174.59511337885445</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-38.795176414897945,174.59165570238244</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-38.794507131525265,174.59193095835477</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-38.793823074895364,174.5921223110537</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-38.79314104786477,174.59232523276296</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-38.792452886353566,174.59249333643135</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-38.791754703809104,174.59261689899748</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-38.7910781971546,174.59287676007085</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-38.79039681024557,174.59309131360212</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-38.78971427897371,174.59329510774526</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-38.789032206717735,174.59350206922645</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-38.78834718404181,174.59368900493382</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-38.78769866732938,174.59396399648665</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-38.78703925857505,174.59415206276205</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-38.786422531209425,174.59459783311652</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-38.78574354254053,174.594827987329</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-38.78507957072813,174.59511337885445</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R357"/>
+  <dimension ref="A1:R359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21826,13 +21826,13 @@
         <v>327.92</v>
       </c>
       <c r="D357" t="n">
-        <v>329.35</v>
+        <v>333.52</v>
       </c>
       <c r="E357" t="n">
         <v>329.75</v>
       </c>
       <c r="F357" t="n">
-        <v>333.25</v>
+        <v>337.66</v>
       </c>
       <c r="G357" t="n">
         <v>340.78</v>
@@ -21859,17 +21859,137 @@
         <v>322.86</v>
       </c>
       <c r="O357" t="n">
-        <v>309.77</v>
+        <v>313.78</v>
       </c>
       <c r="P357" t="n">
         <v>316.65</v>
       </c>
       <c r="Q357" t="n">
-        <v>318.45</v>
+        <v>322.02</v>
       </c>
       <c r="R357" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>334.34</v>
+      </c>
+      <c r="C358" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="D358" t="n">
+        <v>333.36</v>
+      </c>
+      <c r="E358" t="n">
+        <v>329.19</v>
+      </c>
+      <c r="F358" t="n">
+        <v>337.64</v>
+      </c>
+      <c r="G358" t="n">
+        <v>340.33</v>
+      </c>
+      <c r="H358" t="n">
+        <v>332.66</v>
+      </c>
+      <c r="I358" t="n">
+        <v>329.69</v>
+      </c>
+      <c r="J358" t="n">
+        <v>327.25</v>
+      </c>
+      <c r="K358" t="n">
+        <v>325.02</v>
+      </c>
+      <c r="L358" t="n">
+        <v>324.05</v>
+      </c>
+      <c r="M358" t="n">
+        <v>314.64</v>
+      </c>
+      <c r="N358" t="n">
+        <v>322.73</v>
+      </c>
+      <c r="O358" t="n">
+        <v>313.58</v>
+      </c>
+      <c r="P358" t="n">
+        <v>317.15</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>321.75</v>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>335.81</v>
+      </c>
+      <c r="C359" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="D359" t="n">
+        <v>334.53</v>
+      </c>
+      <c r="E359" t="n">
+        <v>330.86</v>
+      </c>
+      <c r="F359" t="n">
+        <v>337.54</v>
+      </c>
+      <c r="G359" t="n">
+        <v>339.76</v>
+      </c>
+      <c r="H359" t="n">
+        <v>332.42</v>
+      </c>
+      <c r="I359" t="n">
+        <v>330.39</v>
+      </c>
+      <c r="J359" t="n">
+        <v>327.19</v>
+      </c>
+      <c r="K359" t="n">
+        <v>325.79</v>
+      </c>
+      <c r="L359" t="n">
+        <v>323.76</v>
+      </c>
+      <c r="M359" t="n">
+        <v>314.87</v>
+      </c>
+      <c r="N359" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="O359" t="n">
+        <v>314.53</v>
+      </c>
+      <c r="P359" t="n">
+        <v>319.36</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21884,7 +22004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B376"/>
+  <dimension ref="A1:B378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25647,6 +25767,26 @@
       </c>
       <c r="B376" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>
@@ -25815,28 +25955,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6323658687134521</v>
+        <v>-0.6283468070340004</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06816081536429586</v>
+        <v>0.06804946744690843</v>
       </c>
       <c r="M2" t="n">
-        <v>9.427032666921797</v>
+        <v>9.406933047738988</v>
       </c>
       <c r="N2" t="n">
-        <v>305.3883299451685</v>
+        <v>303.7461289076347</v>
       </c>
       <c r="O2" t="n">
-        <v>17.47536351396355</v>
+        <v>17.42831400071833</v>
       </c>
       <c r="P2" t="n">
-        <v>347.9872262983155</v>
+        <v>347.9448096023063</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25893,28 +26033,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3484546034381865</v>
+        <v>-0.339601053502796</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K3" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2355698776450035</v>
+        <v>0.2252774494567734</v>
       </c>
       <c r="M3" t="n">
-        <v>3.630982235322842</v>
+        <v>3.656803960826915</v>
       </c>
       <c r="N3" t="n">
-        <v>22.29260209311606</v>
+        <v>22.56574428937239</v>
       </c>
       <c r="O3" t="n">
-        <v>4.721504219326301</v>
+        <v>4.75034149186902</v>
       </c>
       <c r="P3" t="n">
-        <v>329.2598286783386</v>
+        <v>329.1673904281595</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25971,28 +26111,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3176002612714295</v>
+        <v>-0.306978177865652</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1987719462449045</v>
+        <v>0.1866550333553988</v>
       </c>
       <c r="M4" t="n">
-        <v>3.444692356508374</v>
+        <v>3.480308629096307</v>
       </c>
       <c r="N4" t="n">
-        <v>22.94682686497264</v>
+        <v>23.30529022876321</v>
       </c>
       <c r="O4" t="n">
-        <v>4.790284632980867</v>
+        <v>4.827555305614138</v>
       </c>
       <c r="P4" t="n">
-        <v>334.249584822966</v>
+        <v>334.1386288449041</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26049,28 +26189,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6938336922611156</v>
+        <v>-0.6851450926088052</v>
       </c>
       <c r="J5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5224703012573831</v>
+        <v>0.5151376501185803</v>
       </c>
       <c r="M5" t="n">
-        <v>3.917250987860898</v>
+        <v>3.940036708975236</v>
       </c>
       <c r="N5" t="n">
-        <v>24.83187010997232</v>
+        <v>25.07637191637508</v>
       </c>
       <c r="O5" t="n">
-        <v>4.983158647883119</v>
+        <v>5.007631367859966</v>
       </c>
       <c r="P5" t="n">
-        <v>340.0478256274212</v>
+        <v>339.957022885646</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26127,28 +26267,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5268492392406355</v>
+        <v>-0.5193693200766174</v>
       </c>
       <c r="J6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5432465419031258</v>
+        <v>0.5351419130077368</v>
       </c>
       <c r="M6" t="n">
-        <v>2.724387810735494</v>
+        <v>2.746250703423012</v>
       </c>
       <c r="N6" t="n">
-        <v>13.17096112972076</v>
+        <v>13.2986769777324</v>
       </c>
       <c r="O6" t="n">
-        <v>3.629181881598214</v>
+        <v>3.646735112087578</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5541043989777</v>
+        <v>346.4759930801977</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26205,28 +26345,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5375815593935661</v>
+        <v>-0.5359732193250353</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5666551076699651</v>
+        <v>0.5676756504117055</v>
       </c>
       <c r="M7" t="n">
-        <v>2.735356959998388</v>
+        <v>2.728582165349879</v>
       </c>
       <c r="N7" t="n">
-        <v>12.4727862475869</v>
+        <v>12.41652424399567</v>
       </c>
       <c r="O7" t="n">
-        <v>3.531683203174784</v>
+        <v>3.523708876169493</v>
       </c>
       <c r="P7" t="n">
-        <v>352.7052315992531</v>
+        <v>352.6884281061914</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26283,28 +26423,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4204178247446474</v>
+        <v>-0.4193061465520121</v>
       </c>
       <c r="J8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3996963321020772</v>
+        <v>0.4010201206022047</v>
       </c>
       <c r="M8" t="n">
-        <v>2.921927636761279</v>
+        <v>2.911404904191253</v>
       </c>
       <c r="N8" t="n">
-        <v>14.98176413805634</v>
+        <v>14.90434717812763</v>
       </c>
       <c r="O8" t="n">
-        <v>3.870628390591939</v>
+        <v>3.860614870474344</v>
       </c>
       <c r="P8" t="n">
-        <v>342.5806635375027</v>
+        <v>342.5690481368261</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26361,28 +26501,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.635117460395623</v>
+        <v>-0.6278871217345635</v>
       </c>
       <c r="J9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5572899704295643</v>
+        <v>0.550814687892931</v>
       </c>
       <c r="M9" t="n">
-        <v>3.374261039087752</v>
+        <v>3.390400990237581</v>
       </c>
       <c r="N9" t="n">
-        <v>18.08448386707032</v>
+        <v>18.24683796956851</v>
       </c>
       <c r="O9" t="n">
-        <v>4.252585550823207</v>
+        <v>4.271631768957679</v>
       </c>
       <c r="P9" t="n">
-        <v>339.9066316034454</v>
+        <v>339.8310727946783</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26439,28 +26579,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4580493708153058</v>
+        <v>-0.4524009204460218</v>
       </c>
       <c r="J10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4110173565919296</v>
+        <v>0.405450822633055</v>
       </c>
       <c r="M10" t="n">
-        <v>3.125161981606157</v>
+        <v>3.135653897576794</v>
       </c>
       <c r="N10" t="n">
-        <v>16.96784923809906</v>
+        <v>17.03338593141508</v>
       </c>
       <c r="O10" t="n">
-        <v>4.119204927907697</v>
+        <v>4.12715227868019</v>
       </c>
       <c r="P10" t="n">
-        <v>333.917159042057</v>
+        <v>333.858134806242</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26517,28 +26657,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2548431248968056</v>
+        <v>-0.2504446255875349</v>
       </c>
       <c r="J11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2729609873597658</v>
+        <v>0.266336983939367</v>
       </c>
       <c r="M11" t="n">
-        <v>2.217167711758869</v>
+        <v>2.223328315646541</v>
       </c>
       <c r="N11" t="n">
-        <v>9.762540724635494</v>
+        <v>9.80602536691754</v>
       </c>
       <c r="O11" t="n">
-        <v>3.124506476971282</v>
+        <v>3.131457387051202</v>
       </c>
       <c r="P11" t="n">
-        <v>327.9292385399401</v>
+        <v>327.88327122634</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26595,28 +26735,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09701914567227864</v>
+        <v>-0.09379966333794847</v>
       </c>
       <c r="J12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0444825941082766</v>
+        <v>0.04196659100483313</v>
       </c>
       <c r="M12" t="n">
-        <v>2.521886321522935</v>
+        <v>2.522545923392658</v>
       </c>
       <c r="N12" t="n">
-        <v>11.41098851653118</v>
+        <v>11.39945139727978</v>
       </c>
       <c r="O12" t="n">
-        <v>3.37801547014385</v>
+        <v>3.376307361197997</v>
       </c>
       <c r="P12" t="n">
-        <v>323.3905165190126</v>
+        <v>323.3568756665663</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26673,28 +26813,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2758530612156769</v>
+        <v>-0.2715550074675331</v>
       </c>
       <c r="J13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2465885627417058</v>
+        <v>0.2415571788397891</v>
       </c>
       <c r="M13" t="n">
-        <v>2.628711171083166</v>
+        <v>2.639388163619628</v>
       </c>
       <c r="N13" t="n">
-        <v>13.12123684953056</v>
+        <v>13.14083485667474</v>
       </c>
       <c r="O13" t="n">
-        <v>3.622324785207776</v>
+        <v>3.625028945632674</v>
       </c>
       <c r="P13" t="n">
-        <v>317.9269530464531</v>
+        <v>317.8820384283063</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26751,28 +26891,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.356454934031223</v>
+        <v>-0.3489389680282976</v>
       </c>
       <c r="J14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L14" t="n">
-        <v>0.383204650864843</v>
+        <v>0.3700348400581082</v>
       </c>
       <c r="M14" t="n">
-        <v>2.687003558737541</v>
+        <v>2.70648924780507</v>
       </c>
       <c r="N14" t="n">
-        <v>11.54195721157204</v>
+        <v>11.76460337063153</v>
       </c>
       <c r="O14" t="n">
-        <v>3.397345612617598</v>
+        <v>3.429956759294719</v>
       </c>
       <c r="P14" t="n">
-        <v>325.7341174784907</v>
+        <v>325.6555691846314</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26829,28 +26969,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3733240962541868</v>
+        <v>-0.3588131742968065</v>
       </c>
       <c r="J15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2027321248094998</v>
+        <v>0.1871034234189798</v>
       </c>
       <c r="M15" t="n">
-        <v>4.274766971098821</v>
+        <v>4.331512053787462</v>
       </c>
       <c r="N15" t="n">
-        <v>30.93240000656035</v>
+        <v>31.74641956093601</v>
       </c>
       <c r="O15" t="n">
-        <v>5.561690391109555</v>
+        <v>5.634396113243726</v>
       </c>
       <c r="P15" t="n">
-        <v>312.0310238369411</v>
+        <v>311.8794301042288</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26907,28 +27047,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3507919270533607</v>
+        <v>-0.3430291904170569</v>
       </c>
       <c r="J16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2198780680175435</v>
+        <v>0.2120759122840377</v>
       </c>
       <c r="M16" t="n">
-        <v>3.848018799046832</v>
+        <v>3.870932997310358</v>
       </c>
       <c r="N16" t="n">
-        <v>24.63993940724628</v>
+        <v>24.81187705286828</v>
       </c>
       <c r="O16" t="n">
-        <v>4.96386335501354</v>
+        <v>4.981152181259701</v>
       </c>
       <c r="P16" t="n">
-        <v>320.0985135351729</v>
+        <v>320.0173826764882</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26985,28 +27125,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3970300408905354</v>
+        <v>-0.3853234229374153</v>
       </c>
       <c r="J17" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K17" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2355944831351373</v>
+        <v>0.2231750956819483</v>
       </c>
       <c r="M17" t="n">
-        <v>4.178299468040692</v>
+        <v>4.219628201828692</v>
       </c>
       <c r="N17" t="n">
-        <v>28.8645846891118</v>
+        <v>29.33139104198552</v>
       </c>
       <c r="O17" t="n">
-        <v>5.372577099410655</v>
+        <v>5.415846290468878</v>
       </c>
       <c r="P17" t="n">
-        <v>323.6931891982242</v>
+        <v>323.5708898543061</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27044,7 +27184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R357"/>
+  <dimension ref="A1:R359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59797,7 +59937,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>-38.793823074895364,174.5921223110537</t>
+          <t>-38.793814831683115,174.59207547418976</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -59807,7 +59947,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>-38.792452886353566,174.59249333643135</t>
+          <t>-38.79244416879184,174.59244380485157</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -59852,7 +59992,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>-38.786422531209425,174.59459783311652</t>
+          <t>-38.7864106725971,174.59455423070025</t>
         </is>
       </c>
       <c r="P357" t="inlineStr">
@@ -59862,12 +60002,196 @@
       </c>
       <c r="Q357" t="inlineStr">
         <is>
-          <t>-38.78507957072813,174.59511337885445</t>
+          <t>-38.78506901340043,174.59507456143695</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-38.795175663708235,174.5916514341962</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-38.794507348972914,174.5919321938713</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-38.79381514796978,174.59207727128748</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-38.79314215485939,174.5923315225478</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-38.792444208327304,174.59244402948457</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-38.79175553162685,174.59262197028488</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-38.7910800984602,174.59288953970568</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-38.7903980077279,174.59309945967297</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-38.78971547644738,174.59330325374</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-38.78903258924127,174.5935046713949</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-38.78834759982568,174.5936918333512</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-38.78769935431668,174.59396745538456</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-38.78703963030574,174.59415348185934</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-38.786411264049484,174.59455640538403</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-38.78574206391643,174.59482255066771</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-38.78506981185426,174.59507749720765</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-38.79517275778865,174.5916349230555</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-38.794504522152344,174.59191613215714</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-38.79381283512282,174.5920641300108</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-38.79313885364231,174.59231276551142</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-38.792444406004684,174.5924451526495</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-38.79175658019568,174.59262839391576</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-38.79108050227715,174.5928922539645</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-38.790396843508965,174.59309153988187</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-38.78971557623683,174.5933039325729</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-38.789031308618775,174.59349595978756</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-38.78834808213484,174.59369511431538</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-38.78769884461644,174.59396488910548</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-38.78703519813096,174.5941365618541</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-38.786408454650314,174.59454607563643</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-38.78573552839478,174.59479852062742</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-38.785064636689306,174.59505846906546</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R359"/>
+  <dimension ref="A1:R360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21940,7 +21940,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>335.81</v>
+        <v>351.27</v>
       </c>
       <c r="C359" t="n">
         <v>329.24</v>
@@ -21990,6 +21990,66 @@
       <c r="R359" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="C360" t="n">
+        <v>327.23</v>
+      </c>
+      <c r="D360" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="E360" t="n">
+        <v>328.82</v>
+      </c>
+      <c r="F360" t="n">
+        <v>336.64</v>
+      </c>
+      <c r="G360" t="n">
+        <v>338.71</v>
+      </c>
+      <c r="H360" t="n">
+        <v>331.17</v>
+      </c>
+      <c r="I360" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="J360" t="n">
+        <v>325.89</v>
+      </c>
+      <c r="K360" t="n">
+        <v>326.13</v>
+      </c>
+      <c r="L360" t="n">
+        <v>323.02</v>
+      </c>
+      <c r="M360" t="n">
+        <v>314.81</v>
+      </c>
+      <c r="N360" t="n">
+        <v>324.44</v>
+      </c>
+      <c r="O360" t="n">
+        <v>315.49</v>
+      </c>
+      <c r="P360" t="n">
+        <v>320.32</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -22004,7 +22064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B378"/>
+  <dimension ref="A1:B379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25787,6 +25847,16 @@
       </c>
       <c r="B378" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -25955,28 +26025,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6283468070340004</v>
+        <v>-0.603489695702075</v>
       </c>
       <c r="J2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06804946744690843</v>
+        <v>0.06269743157590091</v>
       </c>
       <c r="M2" t="n">
-        <v>9.406933047738988</v>
+        <v>9.588444386721173</v>
       </c>
       <c r="N2" t="n">
-        <v>303.7461289076347</v>
+        <v>306.7150524722966</v>
       </c>
       <c r="O2" t="n">
-        <v>17.42831400071833</v>
+        <v>17.51328217303361</v>
       </c>
       <c r="P2" t="n">
-        <v>347.9448096023063</v>
+        <v>347.6817004534167</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26033,28 +26103,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.339601053502796</v>
+        <v>-0.3359100919650235</v>
       </c>
       <c r="J3" t="n">
+        <v>359</v>
+      </c>
+      <c r="K3" t="n">
         <v>358</v>
       </c>
-      <c r="K3" t="n">
-        <v>357</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2252774494567734</v>
+        <v>0.2213969208402825</v>
       </c>
       <c r="M3" t="n">
-        <v>3.656803960826915</v>
+        <v>3.665623138026427</v>
       </c>
       <c r="N3" t="n">
-        <v>22.56574428937239</v>
+        <v>22.640934568542</v>
       </c>
       <c r="O3" t="n">
-        <v>4.75034149186902</v>
+        <v>4.758249107449294</v>
       </c>
       <c r="P3" t="n">
-        <v>329.1673904281595</v>
+        <v>329.1286953070436</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26111,28 +26181,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.306978177865652</v>
+        <v>-0.3031665088732148</v>
       </c>
       <c r="J4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1866550333553988</v>
+        <v>0.1827882713643664</v>
       </c>
       <c r="M4" t="n">
-        <v>3.480308629096307</v>
+        <v>3.490461619665354</v>
       </c>
       <c r="N4" t="n">
-        <v>23.30529022876321</v>
+        <v>23.3872720874355</v>
       </c>
       <c r="O4" t="n">
-        <v>4.827555305614138</v>
+        <v>4.836038883987131</v>
       </c>
       <c r="P4" t="n">
-        <v>334.1386288449041</v>
+        <v>334.0986315708255</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26189,28 +26259,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6851450926088052</v>
+        <v>-0.6814759742284702</v>
       </c>
       <c r="J5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5151376501185803</v>
+        <v>0.5125010697180374</v>
       </c>
       <c r="M5" t="n">
-        <v>3.940036708975236</v>
+        <v>3.948282223014691</v>
       </c>
       <c r="N5" t="n">
-        <v>25.07637191637508</v>
+        <v>25.14263825460294</v>
       </c>
       <c r="O5" t="n">
-        <v>5.007631367859966</v>
+        <v>5.01424353762389</v>
       </c>
       <c r="P5" t="n">
-        <v>339.957022885646</v>
+        <v>339.91852144867</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26267,28 +26337,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5193693200766174</v>
+        <v>-0.5173171233668182</v>
       </c>
       <c r="J6" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5351419130077368</v>
+        <v>0.5337707751574994</v>
       </c>
       <c r="M6" t="n">
-        <v>2.746250703423012</v>
+        <v>2.74866454649713</v>
       </c>
       <c r="N6" t="n">
-        <v>13.2986769777324</v>
+        <v>13.30421537788845</v>
       </c>
       <c r="O6" t="n">
-        <v>3.646735112087578</v>
+        <v>3.647494397238801</v>
       </c>
       <c r="P6" t="n">
-        <v>346.4759930801977</v>
+        <v>346.45445860949</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26345,28 +26415,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5359732193250353</v>
+        <v>-0.5358543644662619</v>
       </c>
       <c r="J7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5676756504117055</v>
+        <v>0.5689411462695815</v>
       </c>
       <c r="M7" t="n">
-        <v>2.728582165349879</v>
+        <v>2.721610954343108</v>
       </c>
       <c r="N7" t="n">
-        <v>12.41652424399567</v>
+        <v>12.38208065654964</v>
       </c>
       <c r="O7" t="n">
-        <v>3.523708876169493</v>
+        <v>3.518818076648698</v>
       </c>
       <c r="P7" t="n">
-        <v>352.6884281061914</v>
+        <v>352.6871809175264</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26423,28 +26493,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4193061465520121</v>
+        <v>-0.4194545507502269</v>
       </c>
       <c r="J8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4010201206022047</v>
+        <v>0.4025358067597676</v>
       </c>
       <c r="M8" t="n">
-        <v>2.911404904191253</v>
+        <v>2.904098501491807</v>
       </c>
       <c r="N8" t="n">
-        <v>14.90434717812763</v>
+        <v>14.86305357069395</v>
       </c>
       <c r="O8" t="n">
-        <v>3.860614870474344</v>
+        <v>3.855263100061259</v>
       </c>
       <c r="P8" t="n">
-        <v>342.5690481368261</v>
+        <v>342.570605397806</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26501,28 +26571,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6278871217345635</v>
+        <v>-0.6241809780318581</v>
       </c>
       <c r="J9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L9" t="n">
-        <v>0.550814687892931</v>
+        <v>0.5473905222833955</v>
       </c>
       <c r="M9" t="n">
-        <v>3.390400990237581</v>
+        <v>3.398881052543731</v>
       </c>
       <c r="N9" t="n">
-        <v>18.24683796956851</v>
+        <v>18.33488907085117</v>
       </c>
       <c r="O9" t="n">
-        <v>4.271631768957679</v>
+        <v>4.281925860036716</v>
       </c>
       <c r="P9" t="n">
-        <v>339.8310727946783</v>
+        <v>339.7921828370912</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26579,28 +26649,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4524009204460218</v>
+        <v>-0.4503008948440292</v>
       </c>
       <c r="J10" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L10" t="n">
-        <v>0.405450822633055</v>
+        <v>0.403929716573398</v>
       </c>
       <c r="M10" t="n">
-        <v>3.135653897576794</v>
+        <v>3.137242978669103</v>
       </c>
       <c r="N10" t="n">
-        <v>17.03338593141508</v>
+        <v>17.03052922403556</v>
       </c>
       <c r="O10" t="n">
-        <v>4.12715227868019</v>
+        <v>4.126806177182975</v>
       </c>
       <c r="P10" t="n">
-        <v>333.858134806242</v>
+        <v>333.836098449008</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26657,28 +26727,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2504446255875349</v>
+        <v>-0.247889197433701</v>
       </c>
       <c r="J11" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K11" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L11" t="n">
-        <v>0.266336983939367</v>
+        <v>0.2621322627700048</v>
       </c>
       <c r="M11" t="n">
-        <v>2.223328315646541</v>
+        <v>2.228678593494287</v>
       </c>
       <c r="N11" t="n">
-        <v>9.80602536691754</v>
+        <v>9.84473670700347</v>
       </c>
       <c r="O11" t="n">
-        <v>3.131457387051202</v>
+        <v>3.137632340954477</v>
       </c>
       <c r="P11" t="n">
-        <v>327.88327122634</v>
+        <v>327.8564561591189</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26735,28 +26805,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09379966333794847</v>
+        <v>-0.09267575521836896</v>
       </c>
       <c r="J12" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K12" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04196659100483313</v>
+        <v>0.04118488033859335</v>
       </c>
       <c r="M12" t="n">
-        <v>2.522545923392658</v>
+        <v>2.520636816547212</v>
       </c>
       <c r="N12" t="n">
-        <v>11.39945139727978</v>
+        <v>11.38046980047795</v>
       </c>
       <c r="O12" t="n">
-        <v>3.376307361197997</v>
+        <v>3.373495190522428</v>
       </c>
       <c r="P12" t="n">
-        <v>323.3568756665663</v>
+        <v>323.3450820766225</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26813,28 +26883,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2715550074675331</v>
+        <v>-0.2693977505442447</v>
       </c>
       <c r="J13" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K13" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2415571788397891</v>
+        <v>0.2390156519756654</v>
       </c>
       <c r="M13" t="n">
-        <v>2.639388163619628</v>
+        <v>2.64484386491601</v>
       </c>
       <c r="N13" t="n">
-        <v>13.14083485667474</v>
+        <v>13.15128442390076</v>
       </c>
       <c r="O13" t="n">
-        <v>3.625028945632674</v>
+        <v>3.6264699673237</v>
       </c>
       <c r="P13" t="n">
-        <v>317.8820384283063</v>
+        <v>317.8594015213267</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26891,28 +26961,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3489389680282976</v>
+        <v>-0.344742238168545</v>
       </c>
       <c r="J14" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K14" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3700348400581082</v>
+        <v>0.3622252136566235</v>
       </c>
       <c r="M14" t="n">
-        <v>2.70648924780507</v>
+        <v>2.718236235905163</v>
       </c>
       <c r="N14" t="n">
-        <v>11.76460337063153</v>
+        <v>11.90991110988523</v>
       </c>
       <c r="O14" t="n">
-        <v>3.429956759294719</v>
+        <v>3.451073906755001</v>
       </c>
       <c r="P14" t="n">
-        <v>325.6555691846314</v>
+        <v>325.6115313222757</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26969,28 +27039,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3588131742968065</v>
+        <v>-0.3519543508743955</v>
       </c>
       <c r="J15" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K15" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1871034234189798</v>
+        <v>0.179926927006686</v>
       </c>
       <c r="M15" t="n">
-        <v>4.331512053787462</v>
+        <v>4.359043557405016</v>
       </c>
       <c r="N15" t="n">
-        <v>31.74641956093601</v>
+        <v>32.13363999779364</v>
       </c>
       <c r="O15" t="n">
-        <v>5.634396113243726</v>
+        <v>5.668654161068008</v>
       </c>
       <c r="P15" t="n">
-        <v>311.8794301042288</v>
+        <v>311.8074578944625</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27047,28 +27117,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3430291904170569</v>
+        <v>-0.3381193088124473</v>
       </c>
       <c r="J16" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K16" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2120759122840377</v>
+        <v>0.206610251527458</v>
       </c>
       <c r="M16" t="n">
-        <v>3.870932997310358</v>
+        <v>3.888345848324843</v>
       </c>
       <c r="N16" t="n">
-        <v>24.81187705286828</v>
+        <v>24.98650544216504</v>
       </c>
       <c r="O16" t="n">
-        <v>4.981152181259701</v>
+        <v>4.998650362064248</v>
       </c>
       <c r="P16" t="n">
-        <v>320.0173826764882</v>
+        <v>319.9658614450741</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27125,28 +27195,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3853234229374153</v>
+        <v>-0.3797916120003907</v>
       </c>
       <c r="J17" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K17" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2231750956819483</v>
+        <v>0.2173650714695234</v>
       </c>
       <c r="M17" t="n">
-        <v>4.219628201828692</v>
+        <v>4.238901197409986</v>
       </c>
       <c r="N17" t="n">
-        <v>29.33139104198552</v>
+        <v>29.55909023230076</v>
       </c>
       <c r="O17" t="n">
-        <v>5.415846290468878</v>
+        <v>5.43682722111902</v>
       </c>
       <c r="P17" t="n">
-        <v>323.5708898543061</v>
+        <v>323.5128424848629</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27184,7 +27254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R359"/>
+  <dimension ref="A1:R360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60111,7 +60181,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>-38.79517275778865,174.5916349230555</t>
+          <t>-38.79514219606952,174.59146127535314</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -60192,6 +60262,98 @@
       <c r="R359" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-38.79511920541895,174.59133064654637</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-38.79450849551489,174.59193870841304</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-38.793815266577276,174.59207794519912</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-38.79314288626635,174.59233567829858</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-38.79244618510052,174.59245526113432</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-38.7917585117689,174.59264022692042</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-38.79108260548933,174.59290639072958</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-38.7903970264577,174.59309278442043</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-38.78971773834052,174.59331864061966</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-38.7890307431489,174.5934921131039</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-38.78834931285438,174.59370348643108</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-38.78769897758172,174.59396555856958</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-38.787034740615994,174.594134815273</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-38.78640561567756,174.59453563715545</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-38.78573268943358,174.59478808224023</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-38.785063335504475,174.59505368484727</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
